--- a/mock-data/buyer-master-data.xlsx
+++ b/mock-data/buyer-master-data.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">

--- a/mock-data/buyer-master-data.xlsx
+++ b/mock-data/buyer-master-data.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>john.miller@acme.com</t>
+          <t>john.miller@glps.com</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>PUNCH-AC-001</t>
+          <t>PUNCH-GL-001</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>linda.park@acme.com</t>
+          <t>linda.park@glps.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>PUNCH-AC-002</t>
+          <t>PUNCH-GL-002</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>mark.snow@acme.com</t>
+          <t>mark.snow@ekbd.com</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-NE</t>
+          <t>BR-GLP-NE</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>PUNCH-AC-003</t>
+          <t>PUNCH-EK-003</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>sara.lee@globex.com</t>
+          <t>sara.lee@pcbk.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>BR-GLOBEX-WEST</t>
+          <t>BR-PCBK-WEST</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>PUNCH-GX-010</t>
+          <t>PUNCH-PC-010</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>tom.gray@acme.com</t>
+          <t>tom.gray@glps.com</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -877,7 +877,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -935,7 +935,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>PIPE,FLANGE,VALVE,PUMP,GASKET,CHEMICAL</t>
+          <t>CARTRIDGE,DRAIN,VALVE,SHOWERSYS,SEAL,FINISH</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>PIPE,FLANGE,GASKET</t>
+          <t>CARTRIDGE,DRAIN,SEAL</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>PUMP,CHEMICAL,VALVE</t>
+          <t>SHOWERSYS,FINISH,VALVE</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -997,7 +997,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-NE</t>
+          <t>BR-GLP-NE</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>PIPE,FLANGE,VALVE,GASKET</t>
+          <t>CARTRIDGE,DRAIN,VALVE,SEAL</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>BR-GLOBEX-WEST</t>
+          <t>BR-PCBK-WEST</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>PIPE,VALVE,PUMP</t>
+          <t>CARTRIDGE,VALVE,SHOWERSYS</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-NE</t>
+          <t>BR-GLP-NE</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>BR-GLOBEX-WEST</t>
+          <t>BR-PCBK-WEST</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>BR-ACME-MW</t>
+          <t>BR-GLP-MW</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GP-ACME</t>
+          <t>GP-CONT</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Hazardous goods - senior buyers only</t>
+          <t>Hazardous finishes - senior buyers only</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>PUMP</t>
+          <t>SHOWERSYS</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Valves not orderable for maintenance CC</t>
+          <t>Shower valves not orderable for maintenance CC</t>
         </is>
       </c>
     </row>

--- a/mock-data/buyer-master-data.xlsx
+++ b/mock-data/buyer-master-data.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -490,6 +490,8 @@
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -560,6 +562,16 @@
           <t>punchout_id</t>
         </is>
       </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>approver_id</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>approval_threshold_amount</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -620,6 +632,14 @@
           <t>PUNCH-GL-001</t>
         </is>
       </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>APR-501</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>25000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -680,6 +700,14 @@
           <t>PUNCH-GL-002</t>
         </is>
       </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>APR-501</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -740,6 +768,14 @@
           <t>PUNCH-EK-003</t>
         </is>
       </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>APR-502</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>50000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -800,6 +836,14 @@
           <t>PUNCH-PC-010</t>
         </is>
       </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>APR-503</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>75000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -856,10 +900,18 @@
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>APR-501</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mock-data/buyer-master-data.xlsx
+++ b/mock-data/buyer-master-data.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>JUNIOR_BUYER</t>
+          <t>SENIOR_BUYER</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>5000</v>
+        <v>200000</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>5000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="5">
@@ -1026,19 +1026,19 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>CARTRIDGE,DRAIN,SEAL</t>
+          <t>CARTRIDGE,DRAIN,SEAL,VALVE,SHOWERSYS</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>SHOWERSYS,FINISH,VALVE</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2500</v>
+        <v>100000</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>5000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="5">
@@ -1345,7 +1345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1483,82 +1483,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>PV-003</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>SHOWERSYS</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>SKU-SHS-7700</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>RESTRICTED</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>SENIOR_BUYER</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Capital equipment approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>PV-004</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>cost_center</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>CC-MW-200</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>VALVE</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>HIDDEN</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>BUYER</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Shower valves not orderable for maintenance CC</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/mock-data/buyer-master-data.xlsx
+++ b/mock-data/buyer-master-data.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>25000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="4">
